--- a/Q1_Top_50_Suppliers.xlsx
+++ b/Q1_Top_50_Suppliers.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,77 +441,88 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Fulfillment</t>
+          <t>Fulfillment_Rate</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Stability</t>
+          <t>Stability_Index</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Total_Volume</t>
+          <t>Predicted_Trend</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Score</t>
+          <t>Total_Supply</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Final_Score</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>S002</t>
+          <t>S226</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.9955462488573206</v>
+        <v>0.9827237272056394</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1129305983720511</v>
+        <v>0.1368065796809415</v>
       </c>
       <c r="E2" t="n">
-        <v>93659</v>
+        <v>461.2783214552335</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7228418931211891</v>
+        <v>93231</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7214096960625829</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S226</t>
+          <t>S113</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.9827237272056394</v>
+        <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1368065796809415</v>
+        <v>0.1336004216546538</v>
       </c>
       <c r="E3" t="n">
-        <v>93231</v>
+        <v>445.2168925097079</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7227197344195797</v>
+        <v>80114</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7173555055146542</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S389</t>
+          <t>S395</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -520,46 +531,52 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>0.9993769879004383</v>
       </c>
       <c r="D4" t="n">
-        <v>0.1033217343884316</v>
+        <v>0.09157123372504117</v>
       </c>
       <c r="E4" t="n">
-        <v>92838</v>
+        <v>462.9605691939096</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7205101717582237</v>
+        <v>91434</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7155480789018001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>S102</t>
+          <t>S390</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.9909837139239293</v>
+        <v>0.9877116271054905</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1322319898327488</v>
+        <v>0.0654074856866349</v>
       </c>
       <c r="E5" t="n">
-        <v>90786</v>
+        <v>481.7054735469944</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7204862816739735</v>
+        <v>91711</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.7147068965481866</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S260</t>
+          <t>S150</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -571,187 +588,211 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1008800814450681</v>
+        <v>0.0964327037105055</v>
       </c>
       <c r="E6" t="n">
-        <v>92835</v>
+        <v>450.3095549257221</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7197715518639873</v>
+        <v>79163</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.7093768350653036</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S358</t>
+          <t>S401</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.9876613905245423</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1247876953307395</v>
+        <v>0.1303021381609243</v>
       </c>
       <c r="E7" t="n">
-        <v>91413</v>
+        <v>433.7344363617423</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7178717499701941</v>
+        <v>82368</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.709214893826797</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>S219</t>
+          <t>S231</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.9957309039657554</v>
+        <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.06888982087801609</v>
+        <v>0.04947867104130099</v>
       </c>
       <c r="E8" t="n">
-        <v>97495</v>
+        <v>469.5930307673164</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7175525564499059</v>
+        <v>93629</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7073001270662982</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>S079</t>
+          <t>S359</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.9913249554289582</v>
+        <v>0.9971860978021033</v>
       </c>
       <c r="D9" t="n">
-        <v>0.119051458244496</v>
+        <v>0.07502655322783103</v>
       </c>
       <c r="E9" t="n">
-        <v>91190</v>
+        <v>457.5760962285224</v>
       </c>
       <c r="F9" t="n">
-        <v>0.717527443128629</v>
+        <v>91784</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.7063549379063097</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S013</t>
+          <t>S038</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.9973403382038964</v>
+        <v>0.9999124716900513</v>
       </c>
       <c r="D10" t="n">
-        <v>0.1064953649054532</v>
+        <v>0.05181591697212329</v>
       </c>
       <c r="E10" t="n">
-        <v>91122</v>
+        <v>465.6165298732038</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7166294955932321</v>
+        <v>91391</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7054897756894728</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S214</t>
+          <t>S222</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0.08173244818107117</v>
+        <v>0.1315055473094819</v>
       </c>
       <c r="E11" t="n">
-        <v>94103</v>
+        <v>426.9700634993662</v>
       </c>
       <c r="F11" t="n">
-        <v>0.7166156772968832</v>
+        <v>84963</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7053631517801109</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>S047</t>
+          <t>S383</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1528661317237342</v>
+        <v>0.05341759160081494</v>
       </c>
       <c r="E12" t="n">
-        <v>83579</v>
+        <v>463.7770237619866</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7164727509741247</v>
+        <v>91826</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.7048596685534909</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S026</t>
+          <t>S067</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1134040032889696</v>
+        <v>0.07928369660117951</v>
       </c>
       <c r="E13" t="n">
-        <v>89370</v>
+        <v>449.8152947533811</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7164554954495641</v>
+        <v>93729</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.7039243140268777</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S373</t>
+          <t>S081</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -760,46 +801,52 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.9983437858846281</v>
+        <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1054743811225878</v>
+        <v>0.08062341091675451</v>
       </c>
       <c r="E14" t="n">
-        <v>90418</v>
+        <v>440.5960117941862</v>
       </c>
       <c r="F14" t="n">
-        <v>0.715387822997386</v>
+        <v>83260</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.6985845769606203</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>S067</t>
+          <t>S079</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1</v>
+        <v>0.9913249554289582</v>
       </c>
       <c r="D15" t="n">
-        <v>0.07928369660117951</v>
+        <v>0.119051458244496</v>
       </c>
       <c r="E15" t="n">
-        <v>93729</v>
+        <v>425.8146919506704</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7151175917565722</v>
+        <v>91190</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.6974373566278499</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S051</t>
+          <t>S388</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -808,22 +855,25 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.9988781644229849</v>
+        <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.07617607855963149</v>
+        <v>0.1096368109708482</v>
       </c>
       <c r="E16" t="n">
-        <v>94382</v>
+        <v>422.1930050868938</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7149573816660877</v>
+        <v>82824</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.6958274400762738</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S395</t>
+          <t>S339</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -832,118 +882,133 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.9993769879004383</v>
+        <v>0.9920334783587899</v>
       </c>
       <c r="D17" t="n">
-        <v>0.09157123372504117</v>
+        <v>0.1081240013365646</v>
       </c>
       <c r="E17" t="n">
-        <v>91434</v>
+        <v>427.6639495332673</v>
       </c>
       <c r="F17" t="n">
-        <v>0.7138074782550242</v>
+        <v>83681</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.6955942226674656</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S028</t>
+          <t>S093</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C18" t="n">
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.08376207711754846</v>
+        <v>0.05956713456803098</v>
       </c>
       <c r="E18" t="n">
-        <v>92140</v>
+        <v>444.4630595438578</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7132174212980612</v>
+        <v>90872</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.6946760418714413</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S286</t>
+          <t>S331</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.9934623753027526</v>
+        <v>0.9959698032455447</v>
       </c>
       <c r="D19" t="n">
-        <v>0.06271005335365643</v>
+        <v>0.1003397149322517</v>
       </c>
       <c r="E19" t="n">
-        <v>96799</v>
+        <v>426.9814776876913</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7131435912563505</v>
+        <v>83776</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.6944084319754737</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S240</t>
+          <t>S296</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.07620011355545886</v>
+        <v>0.04498567531433395</v>
       </c>
       <c r="E20" t="n">
-        <v>93100</v>
+        <v>449.8944095528279</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7129085158221875</v>
+        <v>94609</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.6936841793247417</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>S222</t>
+          <t>S097</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0.9900194192295422</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1315055473094819</v>
+        <v>0.1281292040257836</v>
       </c>
       <c r="E21" t="n">
-        <v>84963</v>
+        <v>415.999858215131</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7128897861627349</v>
+        <v>87688</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.693525913124909</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>S097</t>
+          <t>S341</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -952,142 +1017,160 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9900194192295422</v>
+        <v>0.9931938214040947</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1281292040257836</v>
+        <v>0.09323796021132635</v>
       </c>
       <c r="E22" t="n">
-        <v>87688</v>
+        <v>430.2669153689012</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7124492363239097</v>
+        <v>89890</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.6932136413357619</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S207</t>
+          <t>S002</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.9934306144991454</v>
+        <v>0.9955462488573206</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1366355134910412</v>
+        <v>0.1129305983720511</v>
       </c>
       <c r="E23" t="n">
-        <v>85440</v>
+        <v>418.9526077565004</v>
       </c>
       <c r="F23" t="n">
-        <v>0.7121178010519247</v>
+        <v>93659</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.6930159978800996</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S310</t>
+          <t>S127</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0.999541704857917</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1425702208555418</v>
+        <v>0.107439966939057</v>
       </c>
       <c r="E24" t="n">
-        <v>82540</v>
+        <v>418.5316637441622</v>
       </c>
       <c r="F24" t="n">
-        <v>0.7112630284919266</v>
+        <v>87240</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.6927048323103437</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>S035</t>
+          <t>S184</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0.03733060356297757</v>
+        <v>0.039869057902023</v>
       </c>
       <c r="E25" t="n">
-        <v>97975</v>
+        <v>449.4918660335538</v>
       </c>
       <c r="F25" t="n">
-        <v>0.7111991810688933</v>
+        <v>93602</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.691898495152388</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>S011</t>
+          <t>S323</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0795047447749615</v>
+        <v>0.04326272173569523</v>
       </c>
       <c r="E26" t="n">
-        <v>91756</v>
+        <v>445.0127499320011</v>
       </c>
       <c r="F26" t="n">
-        <v>0.7111563481581838</v>
+        <v>91396</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.6901270581559076</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>S293</t>
+          <t>S165</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>0.9856283996564444</v>
       </c>
       <c r="D27" t="n">
-        <v>0.06265807774964716</v>
+        <v>0.1208275153783093</v>
       </c>
       <c r="E27" t="n">
-        <v>94123</v>
+        <v>415.6513650410597</v>
       </c>
       <c r="F27" t="n">
-        <v>0.7109341929089718</v>
+        <v>86070</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.6893619616155677</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>S211</t>
+          <t>S225</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1096,46 +1179,52 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0.9816336810034401</v>
       </c>
       <c r="D28" t="n">
-        <v>0.09044584994220706</v>
+        <v>0.1370248199897817</v>
       </c>
       <c r="E28" t="n">
-        <v>89800</v>
+        <v>407.4883881085898</v>
       </c>
       <c r="F28" t="n">
-        <v>0.7104458243881228</v>
+        <v>79904</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.6875394680428181</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>S119</t>
+          <t>S249</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9993280737728542</v>
+        <v>0.9968178202068306</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1155586637881274</v>
+        <v>0.07359434314192104</v>
       </c>
       <c r="E29" t="n">
-        <v>86261</v>
+        <v>427.8857566971648</v>
       </c>
       <c r="F29" t="n">
-        <v>0.710419413517124</v>
+        <v>90216</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.6872872006094075</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>S137</t>
+          <t>S116</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1144,22 +1233,25 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.9881215893401017</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1075301561891808</v>
+        <v>0.1018909523249039</v>
       </c>
       <c r="E30" t="n">
-        <v>90174</v>
+        <v>412.0943317158283</v>
       </c>
       <c r="F30" t="n">
-        <v>0.7103953709986092</v>
+        <v>84885</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.6872143580348951</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>S199</t>
+          <t>S055</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1171,43 +1263,49 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1111427572008189</v>
+        <v>0.02871727505107435</v>
       </c>
       <c r="E31" t="n">
-        <v>86619</v>
+        <v>445.9012408346209</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7101614033276352</v>
+        <v>95119</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.6863167649062807</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>S127</t>
+          <t>S261</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.999541704857917</v>
+        <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>0.107439966939057</v>
+        <v>0.03000161406299851</v>
       </c>
       <c r="E32" t="n">
-        <v>87240</v>
+        <v>442.7176269697969</v>
       </c>
       <c r="F32" t="n">
-        <v>0.7100890890021275</v>
+        <v>93913</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.6847193526655579</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>S294</t>
+          <t>S345</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1219,19 +1317,22 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>0.09352525856525395</v>
+        <v>0.05700241858026012</v>
       </c>
       <c r="E33" t="n">
-        <v>88945</v>
+        <v>429.4280356429799</v>
       </c>
       <c r="F33" t="n">
-        <v>0.7096243037752409</v>
+        <v>92058</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.6845430067345508</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>S014</t>
+          <t>S372</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1240,22 +1341,25 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>0.9886636401586179</v>
       </c>
       <c r="D34" t="n">
-        <v>0.05235103142388131</v>
+        <v>0.1374558502941726</v>
       </c>
       <c r="E34" t="n">
-        <v>94970</v>
+        <v>397.6193843787796</v>
       </c>
       <c r="F34" t="n">
-        <v>0.7095710915144315</v>
+        <v>75787</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.6843344716599379</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>S187</t>
+          <t>S177</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1264,94 +1368,106 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.9965117996613946</v>
+        <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1074381637568029</v>
+        <v>0.07681844187089493</v>
       </c>
       <c r="E35" t="n">
-        <v>87704</v>
+        <v>419.5069012338176</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7095207758523542</v>
+        <v>88583</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.6843090582659798</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>S182</t>
+          <t>S266</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>0.9913346435590383</v>
+        <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1081622041025453</v>
+        <v>0.11894233861617</v>
       </c>
       <c r="E36" t="n">
-        <v>88776</v>
+        <v>399.170583690689</v>
       </c>
       <c r="F36" t="n">
-        <v>0.7093377232501399</v>
+        <v>83988</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.6842810291592292</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>S332</t>
+          <t>S362</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1</v>
+        <v>0.9864556154693455</v>
       </c>
       <c r="D37" t="n">
-        <v>0.07052847335857304</v>
+        <v>0.1119721045570652</v>
       </c>
       <c r="E37" t="n">
-        <v>91998</v>
+        <v>409.7963307378021</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7089574703056072</v>
+        <v>85067</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.6833897843123442</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>S239</t>
+          <t>S332</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>0.9960854654573237</v>
+        <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1018405528141196</v>
+        <v>0.07052847335857304</v>
       </c>
       <c r="E38" t="n">
-        <v>88297</v>
+        <v>421.0165814510669</v>
       </c>
       <c r="F38" t="n">
-        <v>0.7088388383534541</v>
+        <v>91998</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.6833622772179794</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>S175</t>
+          <t>S105</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1360,118 +1476,133 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0.9932134596080718</v>
+        <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>0.08777589587441215</v>
+        <v>0.07382165595409318</v>
       </c>
       <c r="E39" t="n">
-        <v>91030</v>
+        <v>417.1670837746025</v>
       </c>
       <c r="F39" t="n">
-        <v>0.7087624125750352</v>
+        <v>86290</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.681952814142037</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>S031</t>
+          <t>S301</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.997685760086688</v>
+        <v>0.9917246971286726</v>
       </c>
       <c r="D40" t="n">
-        <v>0.09759268546289046</v>
+        <v>0.1196586354772516</v>
       </c>
       <c r="E40" t="n">
-        <v>88377</v>
+        <v>400.2947873805679</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7085279324288302</v>
+        <v>83170</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.6818859367300489</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>S037</t>
+          <t>S066</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>0.9980418068236304</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1044145252460997</v>
+        <v>0.06027278514934642</v>
       </c>
       <c r="E41" t="n">
-        <v>86801</v>
+        <v>424.8050165078096</v>
       </c>
       <c r="F41" t="n">
-        <v>0.7085144570890124</v>
+        <v>83077</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.6818616823216932</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>S359</t>
+          <t>S054</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.9971860978021033</v>
+        <v>0.9789374832304683</v>
       </c>
       <c r="D42" t="n">
-        <v>0.07502655322783103</v>
+        <v>0.1251594848890049</v>
       </c>
       <c r="E42" t="n">
-        <v>91784</v>
+        <v>405.2196297534101</v>
       </c>
       <c r="F42" t="n">
-        <v>0.7084630970332183</v>
+        <v>80267</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.6814884347544743</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>S020</t>
+          <t>S385</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1177307554984368</v>
+        <v>0.06876212083132804</v>
       </c>
       <c r="E43" t="n">
-        <v>84788</v>
+        <v>418.5299621810564</v>
       </c>
       <c r="F43" t="n">
-        <v>0.708400114631159</v>
+        <v>88874</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.6812837368231468</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>S158</t>
+          <t>S360</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1480,184 +1611,208 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.9852348237414011</v>
+        <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1231530451002839</v>
+        <v>0.06754459018814452</v>
       </c>
       <c r="E44" t="n">
-        <v>87479</v>
+        <v>418.4714345445812</v>
       </c>
       <c r="F44" t="n">
-        <v>0.7081374514533502</v>
+        <v>88522</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.6808820273677247</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>S271</t>
+          <t>S227</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>0.9971997916123881</v>
+        <v>0.9998077944983889</v>
       </c>
       <c r="D45" t="n">
-        <v>0.07327560592363025</v>
+        <v>0.08723354726115251</v>
       </c>
       <c r="E45" t="n">
-        <v>91878</v>
+        <v>408.9184107652331</v>
       </c>
       <c r="F45" t="n">
-        <v>0.7081365454322243</v>
+        <v>88430</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.6807623314192883</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>S341</t>
+          <t>S076</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.9931938214040947</v>
+        <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>0.09323796021132635</v>
+        <v>0.09103605730131048</v>
       </c>
       <c r="E46" t="n">
-        <v>89890</v>
+        <v>406.0560834389486</v>
       </c>
       <c r="F46" t="n">
-        <v>0.7080640885077265</v>
+        <v>80604</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.6801973458293507</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>S198</t>
+          <t>S302</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>0.9960148330082472</v>
+        <v>0.9905834770417851</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1372510694322415</v>
+        <v>0.1327098055278387</v>
       </c>
       <c r="E47" t="n">
-        <v>82727</v>
+        <v>390.9877830633633</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7080564296022319</v>
+        <v>79844</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.6795485166111688</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>S111</t>
+          <t>S389</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>0.9963810452993181</v>
+        <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1018960101784437</v>
+        <v>0.1033217343884316</v>
       </c>
       <c r="E48" t="n">
-        <v>87828</v>
+        <v>398.8653965346621</v>
       </c>
       <c r="F48" t="n">
-        <v>0.7080458783952055</v>
+        <v>92838</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.6794047812384907</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>S195</t>
+          <t>S396</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>0.994674510918882</v>
       </c>
       <c r="D49" t="n">
-        <v>0.08686235029619727</v>
+        <v>0.05315560597785085</v>
       </c>
       <c r="E49" t="n">
-        <v>89107</v>
+        <v>426.2790499835066</v>
       </c>
       <c r="F49" t="n">
-        <v>0.7079561279008011</v>
+        <v>90960</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.6792976193799098</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>S068</t>
+          <t>S084</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>0.1028245933454659</v>
+        <v>0.07507867947240088</v>
       </c>
       <c r="E50" t="n">
-        <v>86629</v>
+        <v>411.2677036493689</v>
       </c>
       <c r="F50" t="n">
-        <v>0.7076863675417873</v>
+        <v>85017</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.6786558628055036</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>S064</t>
+          <t>S214</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>0.1311825742110332</v>
+        <v>0.08173244818107117</v>
       </c>
       <c r="E51" t="n">
-        <v>82411</v>
+        <v>407.9848643929004</v>
       </c>
       <c r="F51" t="n">
-        <v>0.7075834020157978</v>
+        <v>94103</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.6786074831706113</v>
       </c>
     </row>
   </sheetData>
